--- a/data/工作流规则_完整分词2.xlsx
+++ b/data/工作流规则_完整分词2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\uv_code_lib\keyword_classifier_by_workflow\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C72710-68FA-46A1-B268-85B65F9852F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95CB402-F3E0-4EA1-8F7E-ABB574B2A959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1815" yWindow="1815" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$287</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$423</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$D$424</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Sheet4!$A$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -1185,13 +1186,7 @@
     <t>playwright</t>
   </si>
   <si>
-    <t>数据+分析</t>
-  </si>
-  <si>
     <t>深度学习</t>
-  </si>
-  <si>
-    <t>数据+开发</t>
   </si>
   <si>
     <t>亚马逊</t>
@@ -1604,6 +1599,14 @@
   </si>
   <si>
     <t>网络工程</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据+分析&lt;库&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据+开发&lt;库&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4861,7 +4864,7 @@
     </row>
     <row r="361" spans="1:2">
       <c r="A361" t="s">
-        <v>373</v>
+        <v>509</v>
       </c>
       <c r="B361" t="s">
         <v>355</v>
@@ -4869,7 +4872,7 @@
     </row>
     <row r="362" spans="1:2">
       <c r="A362" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B362" t="s">
         <v>355</v>
@@ -4877,7 +4880,7 @@
     </row>
     <row r="363" spans="1:2">
       <c r="A363" t="s">
-        <v>375</v>
+        <v>510</v>
       </c>
       <c r="B363" t="s">
         <v>355</v>
@@ -4885,486 +4888,485 @@
     </row>
     <row r="364" spans="1:2">
       <c r="A364" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B364" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="365" spans="1:2">
       <c r="A365" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B365" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="366" spans="1:2">
       <c r="A366" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B366" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B367" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="368" spans="1:2">
       <c r="A368" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B368" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="369" spans="1:2">
       <c r="A369" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B369" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="370" spans="1:2">
       <c r="A370" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B370" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="371" spans="1:2">
       <c r="A371" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B371" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="372" spans="1:2">
       <c r="A372" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B372" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="373" spans="1:2">
       <c r="A373" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B373" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="374" spans="1:2">
       <c r="A374" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B374" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="375" spans="1:2">
       <c r="A375" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B375" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="376" spans="1:2">
       <c r="A376" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B376" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="377" spans="1:2">
       <c r="A377" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B377" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="378" spans="1:2">
       <c r="A378" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B378" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="379" spans="1:2">
       <c r="A379" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B379" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="380" spans="1:2">
       <c r="A380" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B380" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="381" spans="1:2">
       <c r="A381" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B381" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="382" spans="1:2">
       <c r="A382" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B382" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="383" spans="1:2">
       <c r="A383" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B383" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="384" spans="1:2">
       <c r="A384" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B384" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="385" spans="1:2">
       <c r="A385" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B385" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="386" spans="1:2">
       <c r="A386" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B386" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="387" spans="1:2">
       <c r="A387" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B387" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="388" spans="1:2">
       <c r="A388" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B388" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="389" spans="1:2">
       <c r="A389" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B389" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="390" spans="1:2">
       <c r="A390" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B390" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="391" spans="1:2">
       <c r="A391" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B391" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="392" spans="1:2">
       <c r="A392" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B392" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="393" spans="1:2">
       <c r="A393" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B393" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="394" spans="1:2">
       <c r="A394" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B394" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="395" spans="1:2">
       <c r="A395" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B395" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="396" spans="1:2">
       <c r="A396" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B396" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="397" spans="1:2">
       <c r="A397" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B397" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="398" spans="1:2">
       <c r="A398" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B398" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="399" spans="1:2">
       <c r="A399" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B399" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="400" spans="1:2">
       <c r="A400" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B400" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="401" spans="1:2">
       <c r="A401" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B401" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="402" spans="1:2">
       <c r="A402" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B402" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="403" spans="1:2">
       <c r="A403" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B403" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="404" spans="1:2">
       <c r="A404" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B404" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="405" spans="1:2">
       <c r="A405" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B405" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="406" spans="1:2">
       <c r="A406" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B406" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="407" spans="1:2">
       <c r="A407" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B407" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="408" spans="1:2">
       <c r="A408" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B408" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="409" spans="1:2">
       <c r="A409" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B409" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="410" spans="1:2">
       <c r="A410" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B410" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="411" spans="1:2">
       <c r="A411" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B411" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="412" spans="1:2">
       <c r="A412" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B412" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="413" spans="1:2">
       <c r="A413" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B413" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="414" spans="1:2">
       <c r="A414" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B414" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="415" spans="1:2">
       <c r="A415" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B415" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="416" spans="1:2">
       <c r="A416" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B416" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="417" spans="1:2">
       <c r="A417" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B417" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="418" spans="1:2">
       <c r="A418" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B418" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="419" spans="1:2">
       <c r="A419" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B419" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="420" spans="1:2">
       <c r="A420" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B420" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="421" spans="1:2">
       <c r="A421" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B421" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="422" spans="1:2">
       <c r="A422" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B422" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="423" spans="1:2">
       <c r="A423" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B423" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B287" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5374,6 +5376,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247C52B8-9C27-4155-B0D6-E8DC2058C9B6}">
   <dimension ref="A1:D424"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="33.875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
@@ -5386,7 +5391,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -8537,30 +8542,30 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B288" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C288" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D288" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B289" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C289" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D289" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -8574,7 +8579,7 @@
         <v>338</v>
       </c>
       <c r="D290" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -8588,7 +8593,7 @@
         <v>350</v>
       </c>
       <c r="D291" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -8602,7 +8607,7 @@
         <v>369</v>
       </c>
       <c r="D292" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -8616,7 +8621,7 @@
         <v>348</v>
       </c>
       <c r="D293" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -8630,7 +8635,7 @@
         <v>349</v>
       </c>
       <c r="D294" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -8644,7 +8649,7 @@
         <v>326</v>
       </c>
       <c r="D295" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -8658,7 +8663,7 @@
         <v>329</v>
       </c>
       <c r="D296" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -8672,7 +8677,7 @@
         <v>346</v>
       </c>
       <c r="D297" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -8686,7 +8691,7 @@
         <v>312</v>
       </c>
       <c r="D298" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -8700,7 +8705,7 @@
         <v>314</v>
       </c>
       <c r="D299" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -8714,7 +8719,7 @@
         <v>327</v>
       </c>
       <c r="D300" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -8728,7 +8733,7 @@
         <v>339</v>
       </c>
       <c r="D301" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -8742,7 +8747,7 @@
         <v>367</v>
       </c>
       <c r="D302" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -8756,35 +8761,35 @@
         <v>372</v>
       </c>
       <c r="D303" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B304" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C304" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D304" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B305" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C305" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D305" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -8798,7 +8803,7 @@
         <v>320</v>
       </c>
       <c r="D306" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -8812,7 +8817,7 @@
         <v>321</v>
       </c>
       <c r="D307" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -8826,7 +8831,7 @@
         <v>337</v>
       </c>
       <c r="D308" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -8840,21 +8845,21 @@
         <v>351</v>
       </c>
       <c r="D309" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B310" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C310" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D310" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -8868,7 +8873,7 @@
         <v>319</v>
       </c>
       <c r="D311" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -8882,7 +8887,7 @@
         <v>325</v>
       </c>
       <c r="D312" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -8896,7 +8901,7 @@
         <v>331</v>
       </c>
       <c r="D313" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -8910,7 +8915,7 @@
         <v>336</v>
       </c>
       <c r="D314" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -8924,21 +8929,21 @@
         <v>371</v>
       </c>
       <c r="D315" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B316" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C316" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D316" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -8952,7 +8957,7 @@
         <v>313</v>
       </c>
       <c r="D317" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -8966,7 +8971,7 @@
         <v>316</v>
       </c>
       <c r="D318" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -8980,7 +8985,7 @@
         <v>317</v>
       </c>
       <c r="D319" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -8994,7 +8999,7 @@
         <v>324</v>
       </c>
       <c r="D320" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -9008,7 +9013,7 @@
         <v>328</v>
       </c>
       <c r="D321" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -9022,7 +9027,7 @@
         <v>335</v>
       </c>
       <c r="D322" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -9036,7 +9041,7 @@
         <v>352</v>
       </c>
       <c r="D323" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -9050,7 +9055,7 @@
         <v>354</v>
       </c>
       <c r="D324" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -9064,7 +9069,7 @@
         <v>361</v>
       </c>
       <c r="D325" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -9078,7 +9083,7 @@
         <v>366</v>
       </c>
       <c r="D326" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -9092,133 +9097,133 @@
         <v>368</v>
       </c>
       <c r="D327" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B328" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C328" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D328" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B329" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C329" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D329" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B330" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C330" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D330" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B331" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C331" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D331" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B332" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C332" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D332" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="333" spans="1:4">
       <c r="A333" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B333" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C333" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D333" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B334" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C334" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D334" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="335" spans="1:4">
       <c r="A335" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B335" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C335" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D335" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="336" spans="1:4">
       <c r="A336" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B336" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C336" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D336" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -9232,7 +9237,7 @@
         <v>315</v>
       </c>
       <c r="D337" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -9246,7 +9251,7 @@
         <v>332</v>
       </c>
       <c r="D338" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -9260,7 +9265,7 @@
         <v>333</v>
       </c>
       <c r="D339" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -9274,7 +9279,7 @@
         <v>334</v>
       </c>
       <c r="D340" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -9288,7 +9293,7 @@
         <v>347</v>
       </c>
       <c r="D341" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -9302,7 +9307,7 @@
         <v>355</v>
       </c>
       <c r="D342" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -9316,7 +9321,7 @@
         <v>362</v>
       </c>
       <c r="D343" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -9330,7 +9335,7 @@
         <v>364</v>
       </c>
       <c r="D344" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -9344,105 +9349,105 @@
         <v>370</v>
       </c>
       <c r="D345" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="346" spans="1:4">
       <c r="A346" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B346" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C346" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D346" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="347" spans="1:4">
       <c r="A347" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B347" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C347" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D347" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="348" spans="1:4">
       <c r="A348" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B348" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C348" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D348" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B349" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C349" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D349" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="350" spans="1:4">
       <c r="A350" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B350" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C350" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D350" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="351" spans="1:4">
       <c r="A351" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B351" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C351" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D351" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="352" spans="1:4">
       <c r="A352" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B352" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C352" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D352" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -9456,7 +9461,7 @@
         <v>310</v>
       </c>
       <c r="D353" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -9470,7 +9475,7 @@
         <v>311</v>
       </c>
       <c r="D354" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -9484,7 +9489,7 @@
         <v>318</v>
       </c>
       <c r="D355" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -9498,7 +9503,7 @@
         <v>322</v>
       </c>
       <c r="D356" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -9512,7 +9517,7 @@
         <v>323</v>
       </c>
       <c r="D357" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -9526,7 +9531,7 @@
         <v>340</v>
       </c>
       <c r="D358" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -9540,7 +9545,7 @@
         <v>360</v>
       </c>
       <c r="D359" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -9554,7 +9559,7 @@
         <v>363</v>
       </c>
       <c r="D360" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -9568,105 +9573,105 @@
         <v>365</v>
       </c>
       <c r="D361" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="362" spans="1:4">
       <c r="A362" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B362" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C362" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D362" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="363" spans="1:4">
       <c r="A363" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B363" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C363" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D363" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="364" spans="1:4">
       <c r="A364" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B364" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C364" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D364" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="365" spans="1:4">
       <c r="A365" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B365" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C365" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D365" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="366" spans="1:4">
       <c r="A366" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B366" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C366" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D366" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="367" spans="1:4">
       <c r="A367" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B367" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C367" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D367" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B368" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C368" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D368" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -9680,7 +9685,7 @@
         <v>158</v>
       </c>
       <c r="D369" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -9694,7 +9699,7 @@
         <v>330</v>
       </c>
       <c r="D370" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -9708,7 +9713,7 @@
         <v>341</v>
       </c>
       <c r="D371" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -9722,7 +9727,7 @@
         <v>345</v>
       </c>
       <c r="D372" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -9736,7 +9741,7 @@
         <v>353</v>
       </c>
       <c r="D373" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -9750,7 +9755,7 @@
         <v>358</v>
       </c>
       <c r="D374" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -9764,105 +9769,105 @@
         <v>359</v>
       </c>
       <c r="D375" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="376" spans="1:4">
       <c r="A376" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B376" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C376" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D376" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="377" spans="1:4">
       <c r="A377" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B377" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C377" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D377" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="378" spans="1:4">
       <c r="A378" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B378" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C378" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D378" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="379" spans="1:4">
       <c r="A379" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B379" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C379" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D379" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="380" spans="1:4">
       <c r="A380" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B380" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C380" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D380" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="381" spans="1:4">
       <c r="A381" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B381" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C381" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D381" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="382" spans="1:4">
       <c r="A382" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B382" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C382" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D382" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -9876,7 +9881,7 @@
         <v>308</v>
       </c>
       <c r="D383" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -9890,7 +9895,7 @@
         <v>342</v>
       </c>
       <c r="D384" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -9904,133 +9909,133 @@
         <v>356</v>
       </c>
       <c r="D385" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="386" spans="1:4">
       <c r="A386" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B386" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C386" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D386" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="387" spans="1:4">
       <c r="A387" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B387" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C387" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D387" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="388" spans="1:4">
       <c r="A388" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B388" t="s">
+        <v>380</v>
+      </c>
+      <c r="C388" t="s">
         <v>382</v>
       </c>
-      <c r="C388" t="s">
-        <v>384</v>
-      </c>
       <c r="D388" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="389" spans="1:4">
       <c r="A389" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B389" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C389" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D389" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="390" spans="1:4">
       <c r="A390" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C390" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D390" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="391" spans="1:4">
       <c r="A391" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B391" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C391" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D391" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="392" spans="1:4">
       <c r="A392" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B392" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C392" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D392" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="393" spans="1:4">
       <c r="A393" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B393" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C393" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D393" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="394" spans="1:4">
       <c r="A394" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B394" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C394" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D394" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -10044,91 +10049,91 @@
         <v>357</v>
       </c>
       <c r="D395" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="396" spans="1:4">
       <c r="A396" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B396" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C396" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D396" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="397" spans="1:4">
       <c r="A397" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B397" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C397" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D397" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="398" spans="1:4">
       <c r="A398" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B398" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C398" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D398" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="399" spans="1:4">
       <c r="A399" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B399" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C399" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D399" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="400" spans="1:4">
       <c r="A400" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B400" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C400" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D400" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="401" spans="1:4">
       <c r="A401" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B401" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C401" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D401" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -10139,10 +10144,10 @@
         <v>158</v>
       </c>
       <c r="C402" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D402" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -10153,24 +10158,24 @@
         <v>158</v>
       </c>
       <c r="C403" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D403" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B404" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C404" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D404" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -10181,38 +10186,38 @@
         <v>158</v>
       </c>
       <c r="C405" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D405" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B406" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C406" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D406" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="407" spans="1:4">
       <c r="A407" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B407" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C407" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D407" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -10223,10 +10228,10 @@
         <v>158</v>
       </c>
       <c r="C408" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D408" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -10237,10 +10242,10 @@
         <v>158</v>
       </c>
       <c r="C409" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D409" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -10251,10 +10256,10 @@
         <v>158</v>
       </c>
       <c r="C410" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D410" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -10265,10 +10270,10 @@
         <v>158</v>
       </c>
       <c r="C411" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D411" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -10279,136 +10284,136 @@
         <v>158</v>
       </c>
       <c r="C412" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D412" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="413" spans="1:4">
       <c r="A413" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B413" t="s">
         <v>355</v>
       </c>
       <c r="C413" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D413" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="414" spans="1:4">
       <c r="A414" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B414" t="s">
         <v>355</v>
       </c>
       <c r="C414" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D414" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="415" spans="1:4">
       <c r="A415" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B415" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C415" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D415" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="416" spans="1:4">
       <c r="A416" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B416" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C416" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D416" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="417" spans="1:4">
       <c r="A417" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B417" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C417" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D417" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="418" spans="1:4">
       <c r="A418" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B418" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C418" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D418" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="419" spans="1:4">
       <c r="A419" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B419" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C419" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D419" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="420" spans="1:4">
       <c r="A420" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B420" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C420" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D420" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="421" spans="1:4">
       <c r="A421" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B421" t="s">
         <v>355</v>
       </c>
       <c r="C421" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D421" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -10419,10 +10424,10 @@
         <v>158</v>
       </c>
       <c r="C422" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D422" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -10433,27 +10438,28 @@
         <v>158</v>
       </c>
       <c r="C423" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D423" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="424" spans="1:4">
       <c r="A424" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B424" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C424" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D424" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D424" xr:uid="{247C52B8-9C27-4155-B0D6-E8DC2058C9B6}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10487,842 +10493,842 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D4" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B5" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C5" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B6" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C6" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
+        <v>434</v>
+      </c>
+      <c r="B7" t="s">
+        <v>499</v>
+      </c>
+      <c r="C7" t="s">
+        <v>499</v>
+      </c>
+      <c r="D7" t="s">
         <v>436</v>
-      </c>
-      <c r="B7" t="s">
-        <v>501</v>
-      </c>
-      <c r="C7" t="s">
-        <v>501</v>
-      </c>
-      <c r="D7" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B8" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C8" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D8" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B9" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C9" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D9" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B10" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C10" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D10" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B11" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C11" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D11" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B12" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C12" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D12" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B13" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C13" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D13" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B14" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C14" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D14" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B15" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C15" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D15" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B16" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C16" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D16" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B17" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C17" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D17" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B18" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C18" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D18" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B19" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C19" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D19" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B20" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C20" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D20" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B21" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C21" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D21" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B22" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C22" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B23" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C23" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D23" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B24" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C24" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D24" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B25" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C25" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D25" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B26" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C26" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D26" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B27" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C27" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D27" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B28" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C28" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D28" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B29" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C29" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D29" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B30" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C30" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D30" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B31" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C31" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D31" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B32" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C32" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D32" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B33" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C33" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D33" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B34" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C34" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D34" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B35" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C35" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D35" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B36" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C36" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D36" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B37" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C37" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D37" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B38" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C38" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D38" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B39" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C39" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D39" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B40" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C40" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D40" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B41" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C41" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D41" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B42" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C42" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D42" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B43" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C43" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D43" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B44" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C44" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D44" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B45" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C45" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D45" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B46" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C46" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D46" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B47" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C47" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D47" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B48" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C48" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D48" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B49" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C49" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D49" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B50" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C50" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D50" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B51" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C51" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D51" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B52" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C52" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D52" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B53" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C53" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D53" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B54" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C54" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D54" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B55" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C55" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D55" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B56" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C56" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D56" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B57" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C57" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D57" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B58" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C58" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D58" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B59" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C59" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D59" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B60" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C60" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D60" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B61" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C61" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D61" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -11356,138 +11362,138 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D3" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B5" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C5" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D5" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E5" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B6" t="s">
+        <v>499</v>
+      </c>
+      <c r="C6" t="s">
+        <v>499</v>
+      </c>
+      <c r="D6" t="s">
+        <v>466</v>
+      </c>
+      <c r="E6" t="s">
         <v>501</v>
-      </c>
-      <c r="C6" t="s">
-        <v>501</v>
-      </c>
-      <c r="D6" t="s">
-        <v>468</v>
-      </c>
-      <c r="E6" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B7" t="s">
+        <v>499</v>
+      </c>
+      <c r="C7" t="s">
+        <v>499</v>
+      </c>
+      <c r="D7" t="s">
+        <v>467</v>
+      </c>
+      <c r="E7" t="s">
         <v>501</v>
-      </c>
-      <c r="C7" t="s">
-        <v>501</v>
-      </c>
-      <c r="D7" t="s">
-        <v>469</v>
-      </c>
-      <c r="E7" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B8" t="s">
+        <v>499</v>
+      </c>
+      <c r="C8" t="s">
+        <v>499</v>
+      </c>
+      <c r="D8" t="s">
+        <v>468</v>
+      </c>
+      <c r="E8" t="s">
         <v>501</v>
-      </c>
-      <c r="C8" t="s">
-        <v>501</v>
-      </c>
-      <c r="D8" t="s">
-        <v>470</v>
-      </c>
-      <c r="E8" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B9" t="s">
+        <v>499</v>
+      </c>
+      <c r="C9" t="s">
+        <v>499</v>
+      </c>
+      <c r="D9" t="s">
+        <v>469</v>
+      </c>
+      <c r="E9" t="s">
         <v>501</v>
-      </c>
-      <c r="C9" t="s">
-        <v>501</v>
-      </c>
-      <c r="D9" t="s">
-        <v>471</v>
-      </c>
-      <c r="E9" t="s">
-        <v>503</v>
       </c>
     </row>
   </sheetData>

--- a/data/工作流规则_完整分词2.xlsx
+++ b/data/工作流规则_完整分词2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\uv_code_lib\keyword_classifier_by_workflow\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github_code_lib\keyword_classifier_by_workflow\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95CB402-F3E0-4EA1-8F7E-ABB574B2A959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2497FBDC-F3B6-45DB-9833-0D8EC0E600F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1820" yWindow="1820" windowWidth="19200" windowHeight="11170" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2545" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2545" uniqueCount="512">
   <si>
     <t>分类规则</t>
   </si>
@@ -1607,6 +1607,10 @@
   </si>
   <si>
     <t>数据+开发&lt;库&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>全</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1980,7 +1984,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B423"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
@@ -5375,9 +5379,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247C52B8-9C27-4155-B0D6-E8DC2058C9B6}">
   <dimension ref="A1:D424"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="33.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10469,11 +10473,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC50CD3-8FDC-4993-BE63-0C1DF47B9E95}">
   <dimension ref="A1:D61"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="6.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.58203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11341,7 +11345,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9628558E-62AF-41DC-8BEC-B4B5F0397A38}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
@@ -11371,7 +11375,7 @@
         <v>499</v>
       </c>
       <c r="D2" t="s">
-        <v>462</v>
+        <v>511</v>
       </c>
       <c r="E2" t="s">
         <v>500</v>
@@ -11388,7 +11392,7 @@
         <v>499</v>
       </c>
       <c r="D3" t="s">
-        <v>463</v>
+        <v>511</v>
       </c>
       <c r="E3" t="s">
         <v>500</v>
@@ -11405,7 +11409,7 @@
         <v>499</v>
       </c>
       <c r="D4" t="s">
-        <v>464</v>
+        <v>511</v>
       </c>
       <c r="E4" t="s">
         <v>500</v>
@@ -11422,7 +11426,7 @@
         <v>499</v>
       </c>
       <c r="D5" t="s">
-        <v>465</v>
+        <v>511</v>
       </c>
       <c r="E5" t="s">
         <v>500</v>
@@ -11439,7 +11443,7 @@
         <v>499</v>
       </c>
       <c r="D6" t="s">
-        <v>466</v>
+        <v>511</v>
       </c>
       <c r="E6" t="s">
         <v>501</v>
@@ -11456,7 +11460,7 @@
         <v>499</v>
       </c>
       <c r="D7" t="s">
-        <v>467</v>
+        <v>511</v>
       </c>
       <c r="E7" t="s">
         <v>501</v>
@@ -11473,7 +11477,7 @@
         <v>499</v>
       </c>
       <c r="D8" t="s">
-        <v>468</v>
+        <v>511</v>
       </c>
       <c r="E8" t="s">
         <v>501</v>
@@ -11490,7 +11494,7 @@
         <v>499</v>
       </c>
       <c r="D9" t="s">
-        <v>469</v>
+        <v>511</v>
       </c>
       <c r="E9" t="s">
         <v>501</v>
